--- a/data/trans_camb/IP15-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP15-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 17,17</t>
+          <t>-0,29; 18,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 14,38</t>
+          <t>-3,88; 13,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 17,95</t>
+          <t>0,23; 18,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 11,94</t>
+          <t>-7,36; 13,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 5,72</t>
+          <t>-12,93; 5,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 10,87</t>
+          <t>-8,85; 10,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 13,14</t>
+          <t>-1,32; 12,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 5,96</t>
+          <t>-6,04; 7,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 11,33</t>
+          <t>-1,11; 12,1</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 152,23</t>
+          <t>-2,72; 175,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 122,98</t>
+          <t>-21,49; 132,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 165,51</t>
+          <t>0,53; 169,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,81; 67,49</t>
+          <t>-28,28; 78,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,34; 32,05</t>
+          <t>-49,38; 30,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,08; 63,48</t>
+          <t>-33,14; 59,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 84,2</t>
+          <t>-6,49; 86,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,26; 41,64</t>
+          <t>-29,41; 46,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 75,33</t>
+          <t>-4,9; 79,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 13,0</t>
+          <t>-7,82; 12,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,54; -2,38</t>
+          <t>-20,5; -2,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 13,35</t>
+          <t>-7,73; 11,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 0,19</t>
+          <t>-17,57; 1,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 4,84</t>
+          <t>-12,88; 5,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 13,63</t>
+          <t>-6,23; 14,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 3,34</t>
+          <t>-9,61; 3,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,73; -1,12</t>
+          <t>-14,01; -1,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 10,62</t>
+          <t>-4,37; 10,66</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 82,22</t>
+          <t>-29,09; 71,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-69,56; -13,75</t>
+          <t>-71,19; -9,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 78,67</t>
+          <t>-28,51; 73,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-64,83; 2,58</t>
+          <t>-66,8; 10,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,84; 32,42</t>
+          <t>-51,12; 39,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,78; 88,62</t>
+          <t>-26,12; 99,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,02; 18,63</t>
+          <t>-39,23; 19,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,0; -6,13</t>
+          <t>-55,24; -6,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 59,41</t>
+          <t>-17,98; 61,8</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 6,07</t>
+          <t>-12,87; 6,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 7,95</t>
+          <t>-13,24; 6,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 13,01</t>
+          <t>-9,3; 13,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 1,21</t>
+          <t>-17,4; 1,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 0,7</t>
+          <t>-18,02; 1,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 17,4</t>
+          <t>-5,81; 17,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 0,54</t>
+          <t>-12,59; 0,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 0,81</t>
+          <t>-12,12; 1,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 12,12</t>
+          <t>-4,48; 12,94</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-57,45; 55,37</t>
+          <t>-59,96; 63,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,86; 76,13</t>
+          <t>-58,71; 60,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,73; 113,79</t>
+          <t>-46,61; 117,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-62,81; 10,66</t>
+          <t>-65,49; 12,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,52; 4,68</t>
+          <t>-69,17; 12,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,17; 100,35</t>
+          <t>-24,9; 99,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-53,4; 4,33</t>
+          <t>-52,85; 4,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,78; 5,9</t>
+          <t>-52,47; 12,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 74,48</t>
+          <t>-20,77; 77,7</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 10,76</t>
+          <t>-2,67; 11,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 7,88</t>
+          <t>-4,05; 8,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,77; 40,17</t>
+          <t>4,28; 40,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 12,38</t>
+          <t>-0,38; 13,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 3,38</t>
+          <t>-8,54; 3,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 13,79</t>
+          <t>-0,41; 14,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 10,99</t>
+          <t>1,55; 10,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 4,29</t>
+          <t>-4,49; 3,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,14; 24,87</t>
+          <t>4,26; 27,2</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 66,96</t>
+          <t>-11,85; 72,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 50,39</t>
+          <t>-18,35; 56,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,76; 240,9</t>
+          <t>21,57; 256,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 80,08</t>
+          <t>-1,21; 83,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,48; 22,77</t>
+          <t>-38,86; 25,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 84,16</t>
+          <t>-2,08; 91,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,83; 67,61</t>
+          <t>7,14; 61,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,31; 25,46</t>
+          <t>-21,11; 22,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,91; 135,26</t>
+          <t>19,86; 146,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 9,43</t>
+          <t>-6,93; 9,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 10,24</t>
+          <t>-6,83; 9,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 15,11</t>
+          <t>-1,63; 15,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 9,47</t>
+          <t>-7,75; 8,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 6,55</t>
+          <t>-8,51; 6,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 12,04</t>
+          <t>-5,87; 11,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 6,7</t>
+          <t>-4,46; 7,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 5,93</t>
+          <t>-5,2; 6,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 10,58</t>
+          <t>-1,27; 11,33</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,04; 66,12</t>
+          <t>-30,91; 74,86</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,49; 73,24</t>
+          <t>-30,53; 69,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 104,04</t>
+          <t>-7,47; 113,86</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 64,17</t>
+          <t>-34,33; 57,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,7; 44,82</t>
+          <t>-37,45; 42,04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 83,65</t>
+          <t>-24,33; 73,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 42,9</t>
+          <t>-21,24; 48,73</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 37,7</t>
+          <t>-25,0; 39,7</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 65,87</t>
+          <t>-6,32; 73,5</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 13,61</t>
+          <t>-6,14; 13,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,89; 22,91</t>
+          <t>2,26; 22,09</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 17,3</t>
+          <t>-1,38; 18,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 13,65</t>
+          <t>-7,68; 13,06</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 8,31</t>
+          <t>-10,66; 8,73</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 17,47</t>
+          <t>-5,11; 17,82</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 10,61</t>
+          <t>-2,57; 11,0</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 11,26</t>
+          <t>-2,17; 12,37</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 14,27</t>
+          <t>-0,11; 13,9</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-46,28; 240,25</t>
+          <t>-50,28; 199,65</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 369,17</t>
+          <t>12,04; 362,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 311,58</t>
+          <t>-12,19; 312,34</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-34,57; 119,14</t>
+          <t>-38,59; 114,62</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-55,05; 73,62</t>
+          <t>-54,18; 76,64</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-30,19; 158,57</t>
+          <t>-27,77; 152,86</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-19,96; 110,25</t>
+          <t>-17,71; 112,99</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 123,12</t>
+          <t>-13,36; 123,77</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 152,11</t>
+          <t>-2,25; 146,17</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 6,89</t>
+          <t>-0,5; 6,74</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 4,42</t>
+          <t>-2,32; 4,43</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4,71; 20,13</t>
+          <t>4,43; 19,56</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 4,37</t>
+          <t>-2,55; 4,51</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 0,06</t>
+          <t>-7,13; -0,09</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,42; 8,08</t>
+          <t>0,15; 8,46</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,66</t>
+          <t>-0,27; 4,44</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,1</t>
+          <t>-3,55; 1,27</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,56; 11,92</t>
+          <t>3,7; 11,87</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 45,05</t>
+          <t>-2,61; 43,23</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 28,59</t>
+          <t>-11,75; 29,17</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>25,4; 125,61</t>
+          <t>24,5; 121,88</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 24,73</t>
+          <t>-11,59; 25,55</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-30,79; 0,74</t>
+          <t>-32,5; -0,32</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,94; 44,35</t>
+          <t>0,43; 45,75</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 26,73</t>
+          <t>-1,47; 25,45</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 6,03</t>
+          <t>-18,02; 7,25</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>18,06; 66,37</t>
+          <t>17,92; 65,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP15-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP15-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 18,41</t>
+          <t>0,05; 18,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 13,93</t>
+          <t>-4,13; 13,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 18,03</t>
+          <t>-0,4; 17,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 13,74</t>
+          <t>-7,73; 12,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 5,15</t>
+          <t>-13,63; 5,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 10,31</t>
+          <t>-9,0; 11,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 12,72</t>
+          <t>-0,89; 12,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 7,13</t>
+          <t>-5,93; 6,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 12,1</t>
+          <t>-0,74; 12,07</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 175,27</t>
+          <t>-2,38; 164,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 132,31</t>
+          <t>-23,68; 129,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 169,8</t>
+          <t>-3,56; 152,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,28; 78,13</t>
+          <t>-27,53; 74,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,38; 30,02</t>
+          <t>-50,6; 28,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,14; 59,61</t>
+          <t>-33,3; 66,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 86,82</t>
+          <t>-4,44; 79,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,41; 46,28</t>
+          <t>-29,26; 42,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 79,6</t>
+          <t>-3,97; 80,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 12,39</t>
+          <t>-7,33; 12,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,5; -2,67</t>
+          <t>-19,36; -2,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 11,85</t>
+          <t>-7,61; 13,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 1,07</t>
+          <t>-16,99; 1,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 5,45</t>
+          <t>-13,27; 4,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 14,67</t>
+          <t>-6,4; 14,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 3,32</t>
+          <t>-9,39; 4,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,01; -1,07</t>
+          <t>-13,33; -0,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 10,66</t>
+          <t>-4,41; 10,58</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,09; 71,35</t>
+          <t>-27,71; 71,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-71,19; -9,76</t>
+          <t>-70,45; -14,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,51; 73,99</t>
+          <t>-27,76; 80,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-66,8; 10,4</t>
+          <t>-66,0; 13,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,12; 39,0</t>
+          <t>-50,6; 26,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 99,64</t>
+          <t>-25,95; 98,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,23; 19,19</t>
+          <t>-38,28; 22,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,24; -6,07</t>
+          <t>-54,46; -2,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-17,98; 61,8</t>
+          <t>-17,1; 58,87</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 6,48</t>
+          <t>-12,1; 5,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 6,9</t>
+          <t>-12,18; 7,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 13,67</t>
+          <t>-8,41; 13,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 1,95</t>
+          <t>-16,52; 1,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 1,68</t>
+          <t>-17,2; 1,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 17,92</t>
+          <t>-7,12; 17,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 0,52</t>
+          <t>-12,04; 1,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 1,79</t>
+          <t>-12,84; 1,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 12,94</t>
+          <t>-4,95; 12,7</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-59,96; 63,33</t>
+          <t>-58,4; 53,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,71; 60,53</t>
+          <t>-59,11; 76,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 117,55</t>
+          <t>-40,8; 122,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-65,49; 12,6</t>
+          <t>-62,01; 6,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,17; 12,44</t>
+          <t>-64,07; 12,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,9; 99,59</t>
+          <t>-28,8; 94,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-52,85; 4,42</t>
+          <t>-52,88; 8,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-52,47; 12,11</t>
+          <t>-54,78; 7,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-20,77; 77,7</t>
+          <t>-21,87; 78,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 11,31</t>
+          <t>-1,85; 11,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 8,19</t>
+          <t>-4,01; 8,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,28; 40,44</t>
+          <t>3,94; 38,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 13,42</t>
+          <t>0,32; 13,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 3,74</t>
+          <t>-8,22; 3,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 14,03</t>
+          <t>-1,4; 13,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 10,33</t>
+          <t>0,96; 10,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 3,73</t>
+          <t>-4,85; 3,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,26; 27,2</t>
+          <t>4,45; 24,86</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 72,64</t>
+          <t>-8,18; 74,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 56,13</t>
+          <t>-18,71; 52,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,57; 256,54</t>
+          <t>19,19; 248,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 83,94</t>
+          <t>1,49; 82,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,86; 25,15</t>
+          <t>-37,98; 19,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 91,34</t>
+          <t>-6,05; 80,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,14; 61,54</t>
+          <t>4,25; 58,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,11; 22,67</t>
+          <t>-22,35; 24,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,86; 146,54</t>
+          <t>19,93; 146,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 9,98</t>
+          <t>-7,36; 8,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 9,58</t>
+          <t>-6,42; 10,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 15,61</t>
+          <t>-1,62; 15,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 8,92</t>
+          <t>-6,51; 8,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 6,19</t>
+          <t>-8,71; 7,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 11,85</t>
+          <t>-5,2; 11,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 7,18</t>
+          <t>-4,57; 6,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 6,12</t>
+          <t>-4,83; 5,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 11,33</t>
+          <t>-1,29; 11,37</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 74,86</t>
+          <t>-33,04; 62,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 69,91</t>
+          <t>-29,42; 74,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 113,86</t>
+          <t>-9,83; 116,76</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-34,33; 57,24</t>
+          <t>-29,06; 56,26</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,45; 42,04</t>
+          <t>-38,9; 50,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-24,33; 73,34</t>
+          <t>-24,34; 78,26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-21,24; 48,73</t>
+          <t>-21,62; 41,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 39,7</t>
+          <t>-23,03; 34,25</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 73,5</t>
+          <t>-5,97; 72,81</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 13,01</t>
+          <t>-6,8; 12,8</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,26; 22,09</t>
+          <t>1,98; 23,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 18,1</t>
+          <t>-0,91; 17,4</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 13,06</t>
+          <t>-6,8; 13,04</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 8,73</t>
+          <t>-11,21; 9,29</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 17,82</t>
+          <t>-5,37; 16,79</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 11,0</t>
+          <t>-3,4; 10,32</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 12,37</t>
+          <t>-2,16; 12,3</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 13,9</t>
+          <t>-0,13; 14,63</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-50,28; 199,65</t>
+          <t>-52,13; 202,41</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12,04; 362,87</t>
+          <t>8,64; 386,7</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 312,34</t>
+          <t>-11,63; 287,6</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-38,59; 114,62</t>
+          <t>-32,91; 131,82</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-54,18; 76,64</t>
+          <t>-54,77; 84,72</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-27,77; 152,86</t>
+          <t>-27,46; 164,23</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 112,99</t>
+          <t>-20,79; 112,57</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 123,77</t>
+          <t>-13,98; 132,17</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 146,17</t>
+          <t>-4,35; 145,62</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 6,74</t>
+          <t>-0,03; 6,86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 4,43</t>
+          <t>-1,89; 4,59</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4,43; 19,56</t>
+          <t>4,84; 20,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 4,51</t>
+          <t>-2,43; 4,39</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,13; -0,09</t>
+          <t>-6,66; -0,01</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,15; 8,46</t>
+          <t>-0,06; 7,89</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,44</t>
+          <t>-0,34; 4,89</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,27</t>
+          <t>-3,55; 1,28</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,7; 11,87</t>
+          <t>3,75; 11,98</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 43,23</t>
+          <t>-0,33; 43,85</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 29,17</t>
+          <t>-10,33; 30,42</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24,5; 121,88</t>
+          <t>26,19; 119,38</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 25,55</t>
+          <t>-11,09; 24,63</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-32,5; -0,32</t>
+          <t>-30,42; 0,69</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,43; 45,75</t>
+          <t>-0,29; 42,77</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 25,45</t>
+          <t>-1,75; 28,21</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 7,25</t>
+          <t>-18,17; 7,39</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>17,92; 65,09</t>
+          <t>18,5; 65,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP15-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP15-Clase-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,68</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-4,22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,64</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>8,72</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4,53</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,68</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-4,22</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>9,4</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,23</t>
+          <t>5,64</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 18,49</t>
+          <t>-8,44; 11,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 13,7</t>
+          <t>-13,99; 5,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 17,29</t>
+          <t>-7,77; 11,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 12,8</t>
+          <t>0,14; 17,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 5,07</t>
+          <t>-4,13; 14,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 11,14</t>
+          <t>1,4; 18,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 12,27</t>
+          <t>-0,89; 13,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 6,79</t>
+          <t>-5,89; 5,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 12,07</t>
+          <t>-0,78; 11,88</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12,18%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-19,19%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,48%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>60,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>31,15%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>63,64%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12,18%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-19,19%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 164,41</t>
+          <t>-31,81; 67,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,68; 129,77</t>
+          <t>-53,34; 32,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 152,71</t>
+          <t>-29,94; 73,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 74,28</t>
+          <t>0,39; 152,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,6; 28,95</t>
+          <t>-26,73; 122,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,3; 66,87</t>
+          <t>7,54; 168,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 79,34</t>
+          <t>-4,12; 84,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,26; 42,29</t>
+          <t>-28,26; 41,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 80,09</t>
+          <t>-2,77; 81,44</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-8,28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-3,87</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,98</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-10,89</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,51</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-8,28</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,87</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,81</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,16</t>
+          <t>2,75</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 12,61</t>
+          <t>-16,81; 0,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,36; -2,77</t>
+          <t>-13,8; 4,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 13,59</t>
+          <t>-6,0; 13,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 1,55</t>
+          <t>-7,54; 13,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 4,18</t>
+          <t>-19,54; -2,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 14,84</t>
+          <t>-9,28; 12,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 4,11</t>
+          <t>-10,12; 3,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,33; -0,46</t>
+          <t>-13,73; -1,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 10,58</t>
+          <t>-4,21; 10,22</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-39,87%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-18,61%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19,18%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>10,45%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-48,96%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11,31%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-39,87%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-18,61%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,71; 71,45</t>
+          <t>-64,83; 2,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,45; -14,48</t>
+          <t>-51,84; 32,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 80,55</t>
+          <t>-23,98; 90,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-66,0; 13,15</t>
+          <t>-28,99; 82,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,6; 26,59</t>
+          <t>-69,56; -13,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,95; 98,41</t>
+          <t>-34,97; 71,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,28; 22,83</t>
+          <t>-40,02; 18,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,46; -2,68</t>
+          <t>-55,0; -6,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 58,87</t>
+          <t>-17,2; 58,27</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-7,74</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-8,49</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,29</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-3,17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-2,18</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,02</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-7,74</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-8,49</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,99</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>2,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 5,36</t>
+          <t>-16,83; 1,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 7,77</t>
+          <t>-18,08; 0,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 13,26</t>
+          <t>-7,32; 16,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 1,19</t>
+          <t>-12,51; 6,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 1,39</t>
+          <t>-11,99; 7,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 17,68</t>
+          <t>-10,35; 12,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 1,04</t>
+          <t>-12,3; 0,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 1,09</t>
+          <t>-12,76; 0,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 12,7</t>
+          <t>-5,89; 11,06</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-35,02%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-38,41%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19,4%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-19,24%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-13,23%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-35,02%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-38,41%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-58,4; 53,49</t>
+          <t>-62,81; 10,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-59,11; 76,86</t>
+          <t>-67,52; 4,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,8; 122,34</t>
+          <t>-29,33; 94,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-62,01; 6,64</t>
+          <t>-57,45; 55,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,07; 12,54</t>
+          <t>-55,86; 76,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,8; 94,4</t>
+          <t>-46,68; 100,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-52,88; 8,58</t>
+          <t>-53,4; 4,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,78; 7,63</t>
+          <t>-54,78; 5,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-21,87; 78,25</t>
+          <t>-26,76; 66,79</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6,63</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,82</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5,44</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,83</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,02</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>16,26</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6,63</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,82</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,39</t>
+          <t>5,02</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,32</t>
+          <t>5,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 11,43</t>
+          <t>-0,56; 12,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 8,06</t>
+          <t>-8,7; 3,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,94; 38,94</t>
+          <t>-2,25; 13,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 13,39</t>
+          <t>-1,76; 10,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 3,19</t>
+          <t>-4,28; 7,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 13,42</t>
+          <t>-2,59; 12,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 10,1</t>
+          <t>1,52; 10,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 3,99</t>
+          <t>-4,45; 4,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 24,86</t>
+          <t>0,58; 10,98</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>34,54%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-14,7%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>28,33%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>25,71%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>10,76%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>86,62%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34,54%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-14,7%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 74,42</t>
+          <t>-2,66; 80,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 52,05</t>
+          <t>-39,48; 22,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19,19; 248,28</t>
+          <t>-11,04; 79,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,49; 82,81</t>
+          <t>-8,77; 66,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,98; 19,42</t>
+          <t>-20,11; 50,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 80,66</t>
+          <t>-11,56; 76,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,25; 58,64</t>
+          <t>6,83; 67,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,35; 24,2</t>
+          <t>-21,31; 25,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,93; 146,42</t>
+          <t>2,82; 65,81</t>
         </is>
       </c>
     </row>
@@ -1493,27 +1493,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>-0,84</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2,93</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1,44</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>6,83</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,1</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,84</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,35</t>
+          <t>6,17</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,82</t>
+          <t>4,37</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 8,52</t>
+          <t>-6,75; 9,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 10,03</t>
+          <t>-8,61; 6,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 15,93</t>
+          <t>-4,48; 11,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 8,42</t>
+          <t>-6,7; 9,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 7,26</t>
+          <t>-6,65; 10,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 11,47</t>
+          <t>-2,52; 14,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 6,44</t>
+          <t>-4,34; 6,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 5,33</t>
+          <t>-5,86; 5,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 11,37</t>
+          <t>-1,48; 10,1</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-4,48%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>15,58%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>6,05%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>7,95%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>37,7%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-4,48%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,04; 62,46</t>
+          <t>-30,02; 64,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-29,42; 74,04</t>
+          <t>-37,7; 44,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 116,76</t>
+          <t>-21,36; 82,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 56,26</t>
+          <t>-30,04; 66,12</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-38,9; 50,5</t>
+          <t>-30,49; 73,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 78,26</t>
+          <t>-11,71; 100,23</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-21,62; 41,03</t>
+          <t>-20,61; 42,9</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 34,25</t>
+          <t>-27,02; 37,7</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 72,81</t>
+          <t>-7,69; 62,67</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>3,17</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-1,24</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5,01</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>3,09</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>11,33</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>7,74</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3,17</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,59</t>
+          <t>7,7</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>6,38</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 12,8</t>
+          <t>-6,89; 13,65</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,98; 23,0</t>
+          <t>-11,55; 8,31</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 17,4</t>
+          <t>-5,77; 17,16</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 13,04</t>
+          <t>-5,85; 13,61</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 9,29</t>
+          <t>0,89; 22,91</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 16,79</t>
+          <t>-1,05; 17,79</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 10,32</t>
+          <t>-3,13; 10,61</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 12,3</t>
+          <t>-2,1; 11,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 14,63</t>
+          <t>-0,81; 13,78</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>20,24%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-7,94%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>31,99%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>30,94%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>113,31%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>77,46%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>20,24%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-7,94%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-52,13; 202,41</t>
+          <t>-34,57; 119,14</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8,64; 386,7</t>
+          <t>-55,05; 73,62</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 287,6</t>
+          <t>-31,43; 150,98</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-32,91; 131,82</t>
+          <t>-46,28; 240,25</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-54,77; 84,72</t>
+          <t>-0,19; 369,17</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 164,23</t>
+          <t>-9,69; 320,11</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 112,57</t>
+          <t>-19,96; 110,25</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 132,17</t>
+          <t>-13,43; 123,12</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 145,62</t>
+          <t>-8,19; 145,76</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,83</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-3,27</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>3,83</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>3,4</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>9,65</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,83</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-3,27</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,78</t>
+          <t>4,66</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 6,86</t>
+          <t>-2,68; 4,37</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 4,59</t>
+          <t>-6,71; 0,06</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4,84; 20,51</t>
+          <t>0,22; 7,78</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 4,39</t>
+          <t>-0,32; 6,89</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,66; -0,01</t>
+          <t>-2,27; 4,42</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 7,89</t>
+          <t>1,62; 9,19</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,89</t>
+          <t>-0,26; 4,66</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,28</t>
+          <t>-3,49; 1,1</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,75; 11,98</t>
+          <t>1,98; 7,27</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-16,56%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>19,81%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>6,48%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>56,17%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-16,56%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 43,85</t>
+          <t>-12,47; 24,73</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 30,42</t>
+          <t>-30,79; 0,74</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26,19; 119,38</t>
+          <t>0,8; 42,79</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 24,63</t>
+          <t>-1,67; 45,05</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-30,42; 0,69</t>
+          <t>-12,03; 28,59</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 42,77</t>
+          <t>8,39; 57,98</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 28,21</t>
+          <t>-1,45; 26,73</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 7,39</t>
+          <t>-18,26; 6,03</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>18,5; 65,44</t>
+          <t>9,94; 42,37</t>
         </is>
       </c>
     </row>
